--- a/ssp_modeling/cb/cb_cost_factors/cb_config_params.xlsx
+++ b/ssp_modeling/cb/cb_cost_factors/cb_config_params.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_uganda_data/ssp_modeling/cb/cb_cost_factors/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94F8C5A-9725-C048-B2D5-0DA8B70844D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946CE2F9-1745-BB47-B535-5A2E056ED382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="-7260" windowWidth="51200" windowHeight="28300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,20 @@
     <sheet name="attribute_dim_time_period" sheetId="16" r:id="rId16"/>
     <sheet name="attribute_transformation_code" sheetId="17" r:id="rId17"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -6581,6 +6594,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E209"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="58.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -18894,79 +18910,79 @@
         <v>706</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
+    <row r="69" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="C69">
-        <v>-5.2</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="C69" s="3">
+        <v>-0.05</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="E69">
-        <v>1</v>
-      </c>
-      <c r="F69" t="s">
+      <c r="E69" s="3">
+        <v>1</v>
+      </c>
+      <c r="F69" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="G69" t="b">
+      <c r="G69" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H69" t="s">
+      <c r="H69" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="I69" t="s">
+      <c r="I69" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="J69" t="s">
+      <c r="J69" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="K69" t="s">
+      <c r="K69" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="L69" t="s">
+      <c r="L69" s="3" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
+    <row r="70" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="C70">
-        <v>-0.17</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="C70" s="3">
+        <v>-0.1</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="E70">
-        <v>1</v>
-      </c>
-      <c r="F70" t="s">
+      <c r="E70" s="3">
+        <v>1</v>
+      </c>
+      <c r="F70" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="G70" t="b">
+      <c r="G70" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="H70" t="s">
+      <c r="H70" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="I70" t="s">
+      <c r="I70" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="J70" t="s">
+      <c r="J70" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="K70" t="s">
+      <c r="K70" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="L70" t="s">
+      <c r="L70" s="3" t="s">
         <v>706</v>
       </c>
     </row>

--- a/ssp_modeling/cb/cb_cost_factors/cb_config_params.xlsx
+++ b/ssp_modeling/cb/cb_cost_factors/cb_config_params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_uganda_data/ssp_modeling/cb/cb_cost_factors/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946CE2F9-1745-BB47-B535-5A2E056ED382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7FF8D9-FE59-144B-AC42-03C26E16E16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-720" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -6595,7 +6595,11 @@
   <dimension ref="A1:E209"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="58.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="59" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -10163,6 +10167,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -10481,6 +10490,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -10601,6 +10615,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -10691,6 +10710,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -10997,6 +11021,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="59.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -11238,6 +11267,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:E217"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -14937,6 +14972,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -15243,6 +15283,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="44.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="255.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -16324,6 +16370,9 @@
   <cols>
     <col min="1" max="1" width="58.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="48.5" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="56" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
@@ -22422,9 +22471,10 @@
     <col min="1" max="1" width="42.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="44.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="37.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.1640625" customWidth="1"/>
+    <col min="8" max="8" width="84.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="9" bestFit="1" customWidth="1"/>
@@ -24789,6 +24839,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -25003,6 +25059,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -25343,6 +25404,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -25649,6 +25715,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -25883,6 +25954,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.33203125" customWidth="1"/>
+    <col min="10" max="10" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -26053,6 +26132,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">

--- a/ssp_modeling/cb/cb_cost_factors/cb_config_params.xlsx
+++ b/ssp_modeling/cb/cb_cost_factors/cb_config_params.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_uganda_data/ssp_modeling/cb/cb_cost_factors/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7FF8D9-FE59-144B-AC42-03C26E16E16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C64E38-6D79-D448-9A39-82F818125857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-720" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -19005,7 +19005,8 @@
         <v>514</v>
       </c>
       <c r="C70" s="3">
-        <v>-0.1</v>
+        <f>-0.1/10</f>
+        <v>-0.01</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>598</v>

--- a/ssp_modeling/cb/cb_cost_factors/cb_config_params.xlsx
+++ b/ssp_modeling/cb/cb_cost_factors/cb_config_params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10921"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_uganda_data/ssp_modeling/cb/cb_cost_factors/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C64E38-6D79-D448-9A39-82F818125857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CFFCD7-34BF-8B4F-A3DD-FF52BCDAB7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38560" yWindow="-5840" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -2479,9 +2479,6 @@
     <t>$/ton waste avoided</t>
   </si>
   <si>
-    <t>$/ton CO2e</t>
-  </si>
-  <si>
     <t>$/acre</t>
   </si>
   <si>
@@ -6205,6 +6202,9 @@
   </si>
   <si>
     <t>Affects both INEN and IPPU.</t>
+  </si>
+  <si>
+    <t>$/MTCO2e</t>
   </si>
 </sst>
 </file>
@@ -10175,18 +10175,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1008</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B2">
         <v>0.84272816699999997</v>
@@ -10197,7 +10197,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B3">
         <v>0.125</v>
@@ -10208,7 +10208,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B4">
         <v>0.125</v>
@@ -10219,7 +10219,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B5">
         <v>0.125</v>
@@ -10230,7 +10230,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B6">
         <v>0.507139381</v>
@@ -10241,7 +10241,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B7">
         <v>0.39353668600000002</v>
@@ -10252,7 +10252,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B8">
         <v>0.150650433</v>
@@ -10263,7 +10263,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B9">
         <v>0.125</v>
@@ -10274,7 +10274,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B10">
         <v>0.125</v>
@@ -10285,7 +10285,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B11">
         <v>0.125</v>
@@ -10296,7 +10296,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B12">
         <v>0.125</v>
@@ -10307,7 +10307,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B13">
         <v>0.125</v>
@@ -10318,7 +10318,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B14">
         <v>0.125</v>
@@ -10329,7 +10329,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B15">
         <v>0.125</v>
@@ -10340,7 +10340,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B16">
         <v>0.125</v>
@@ -10351,7 +10351,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B17">
         <v>0.125</v>
@@ -10362,7 +10362,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B18">
         <v>0.125</v>
@@ -10373,7 +10373,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B19">
         <v>0.125</v>
@@ -10384,7 +10384,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B20">
         <v>0.125</v>
@@ -10395,7 +10395,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B21">
         <v>0.125</v>
@@ -10406,7 +10406,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B22">
         <v>0.497929609</v>
@@ -10417,7 +10417,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B23">
         <v>0.125</v>
@@ -10428,7 +10428,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B24">
         <v>0.125</v>
@@ -10439,7 +10439,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B25">
         <v>0.125</v>
@@ -10450,7 +10450,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B26">
         <v>0.70956093899999995</v>
@@ -10461,7 +10461,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B27">
         <v>0.125</v>
@@ -10472,7 +10472,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B28">
         <v>0.125</v>
@@ -10498,13 +10498,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1010</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -10623,10 +10623,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -10718,10 +10718,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -11029,128 +11029,128 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>439</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B2" t="s">
         <v>453</v>
       </c>
       <c r="C2" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B3" t="s">
         <v>453</v>
       </c>
       <c r="C3" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B4" t="s">
         <v>448</v>
       </c>
       <c r="C4" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B5" t="s">
         <v>447</v>
       </c>
       <c r="C5" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B6" t="s">
         <v>453</v>
       </c>
       <c r="C6" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B7" t="s">
         <v>453</v>
       </c>
       <c r="C7" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B8" t="s">
         <v>453</v>
       </c>
       <c r="C8" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B9" t="s">
         <v>449</v>
       </c>
       <c r="C9" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B10" t="s">
         <v>447</v>
       </c>
       <c r="C10" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B11" t="s">
         <v>448</v>
       </c>
       <c r="C11" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B12" t="s">
         <v>452</v>
@@ -11161,7 +11161,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B13" t="s">
         <v>452</v>
@@ -11172,7 +11172,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B14" t="s">
         <v>451</v>
@@ -11183,7 +11183,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B15" t="s">
         <v>450</v>
@@ -11194,7 +11194,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B16" t="s">
         <v>451</v>
@@ -11205,7 +11205,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B17" t="s">
         <v>452</v>
@@ -11216,7 +11216,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B18" t="s">
         <v>452</v>
@@ -11227,7 +11227,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B19" t="s">
         <v>451</v>
@@ -11238,7 +11238,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B20" t="s">
         <v>450</v>
@@ -11249,7 +11249,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B21" t="s">
         <v>451</v>
@@ -11276,3691 +11276,3691 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1036</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1037</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1038</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B2" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C2" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="D2" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="E2" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B3" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C3" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="D3" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="E3" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B4" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="C4" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="D4" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="E4" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B5" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="C5" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="D5" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="E5" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B6" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="C6" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="D6" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="E6" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B7" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="C7" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="D7" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="E7" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B8" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="C8" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="D8" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="E8" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B9" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="C9" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="D9" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="E9" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B10" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="C10" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="D10" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="E10" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B11" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="C11" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="D11" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="E11" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B12" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C12" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="D12" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="E12" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B13" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="C13" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="D13" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="E13" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B14" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="C14" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="D14" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="E14" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B15" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="C15" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="D15" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="E15" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B16" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="C16" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="D16" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="E16" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B17" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C17" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="D17" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="E17" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B18" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C18" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="D18" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="E18" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B19" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C19" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="D19" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="E19" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B20" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="C20" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="D20" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="E20" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B21" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C21" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="D21" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="E21" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B22" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="C22" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="D22" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="E22" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B23" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="C23" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="D23" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="E23" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B24" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C24" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="D24" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="E24" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B25" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="C25" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="D25" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="E25" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B26" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="C26" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="D26" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="E26" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B27" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C27" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="D27" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="E27" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B28" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="C28" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="D28" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="E28" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B29" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="C29" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="D29" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="E29" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B30" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C30" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="D30" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="E30" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B31" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="C31" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="D31" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="E31" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B32" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="C32" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="D32" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="E32" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B33" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C33" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="D33" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="E33" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B34" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="C34" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="D34" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="E34" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B35" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="C35" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="D35" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="E35" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B36" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C36" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="D36" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="E36" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B37" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C37" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="D37" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="E37" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B38" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C38" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="D38" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="E38" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B39" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C39" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="D39" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="E39" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B40" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C40" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="D40" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="E40" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B41" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="C41" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="D41" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="E41" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B42" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C42" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D42" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="E42" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B43" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="C43" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="D43" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="E43" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B44" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="C44" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="D44" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="E44" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B45" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="C45" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="D45" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="E45" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B46" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="C46" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="D46" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="E46" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B47" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C47" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="D47" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="E47" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B48" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C48" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="D48" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="E48" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B49" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C49" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="D49" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="E49" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B50" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="C50" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="D50" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="E50" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B51" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="C51" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="D51" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E51" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B52" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C52" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="D52" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="E52" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B53" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C53" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D53" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="E53" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B54" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C54" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="D54" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="E54" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B55" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C55" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="D55" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="E55" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B56" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C56" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="D56" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="E56" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B57" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="C57" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="D57" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="E57" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B58" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="C58" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="D58" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="E58" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B59" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="C59" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="D59" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="E59" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B60" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C60" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="D60" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="E60" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B61" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="C61" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="D61" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E61" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B62" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C62" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="D62" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="E62" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B63" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C63" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="D63" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="E63" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B64" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="C64" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="D64" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="E64" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B65" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C65" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D65" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="E65" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B66" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="C66" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="D66" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="E66" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B67" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="C67" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D67" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="E67" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B68" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="C68" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="D68" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="E68" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B69" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C69" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="D69" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="E69" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B70" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C70" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D70" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="E70" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B71" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="C71" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="D71" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="E71" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B72" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="C72" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="D72" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="E72" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B73" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="C73" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="D73" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="E73" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B74" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="C74" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="D74" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="E74" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B75" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C75" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="D75" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="E75" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B76" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C76" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="D76" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="E76" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B77" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="C77" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="D77" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="E77" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B78" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="C78" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="D78" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="E78" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B79" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="C79" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="D79" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="E79" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B80" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="C80" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="D80" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="E80" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B81" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="C81" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="D81" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="E81" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B82" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="C82" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="D82" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="E82" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B83" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="C83" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="D83" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="E83" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B84" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="C84" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="D84" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="E84" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B85" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C85" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="D85" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="E85" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B86" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C86" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="D86" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="E86" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B87" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C87" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="D87" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="E87" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="B88" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="C88" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="D88" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="E88" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B89" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C89" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="D89" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="E89" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B90" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C90" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="D90" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="E90" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B91" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="C91" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="D91" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="E91" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B92" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="C92" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="D92" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="E92" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B93" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C93" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="D93" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="E93" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B94" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C94" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="D94" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="E94" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B95" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="C95" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="D95" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="E95" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B96" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C96" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="D96" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="E96" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B97" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="C97" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="D97" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="E97" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B98" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="C98" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="D98" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="E98" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B99" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="C99" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="D99" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="E99" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="B100" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="C100" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="D100" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="E100" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B101" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C101" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="D101" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="E101" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B102" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="C102" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="D102" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="E102" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="B103" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="C103" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="D103" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="E103" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="B104" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C104" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="D104" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="E104" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B105" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C105" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="D105" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="E105" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B106" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="C106" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="D106" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="E106" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B107" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="C107" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="D107" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="E107" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B108" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C108" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="D108" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="E108" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B109" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="C109" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="D109" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="E109" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B110" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="C110" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="D110" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="E110" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B111" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="C111" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="D111" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="E111" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B112" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="C112" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="D112" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="E112" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B113" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="C113" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="D113" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="E113" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B114" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="C114" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="D114" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="E114" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B115" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="C115" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="D115" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="E115" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B116" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="C116" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="D116" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="E116" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B117" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="C117" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="D117" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="E117" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B118" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="C118" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="D118" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="E118" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B119" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="C119" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="D119" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="E119" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="B120" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="C120" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="D120" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="E120" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="B121" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="C121" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="D121" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="E121" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B122" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="C122" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="D122" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="E122" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B123" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C123" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="D123" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="E123" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B124" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="C124" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="D124" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="E124" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B125" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="C125" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="D125" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="E125" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B126" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="C126" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="D126" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="E126" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B127" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C127" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="D127" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="E127" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B128" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C128" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="D128" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="E128" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B129" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="C129" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="D129" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="E129" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B130" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C130" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="D130" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="E130" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B131" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C131" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="D131" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="E131" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B132" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="C132" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="D132" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="E132" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B133" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="C133" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="D133" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="E133" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B134" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="C134" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="D134" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="E134" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B135" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="C135" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="D135" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="E135" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B136" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="C136" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="D136" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="E136" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B137" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="C137" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="D137" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="E137" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B138" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="C138" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="D138" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="E138" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B139" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="C139" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="D139" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="E139" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B140" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C140" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="D140" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="E140" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B141" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="C141" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="D141" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="E141" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B142" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="C142" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="D142" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="E142" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B143" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="C143" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="D143" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="E143" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B144" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="C144" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="D144" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="E144" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B145" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="C145" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="D145" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="E145" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B146" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="C146" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="D146" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="E146" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B147" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="C147" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="D147" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="E147" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B148" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="C148" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="D148" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="E148" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B149" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="C149" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="D149" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="E149" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B150" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="C150" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="D150" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="E150" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B151" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="C151" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="D151" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="E151" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B152" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="C152" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="D152" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="E152" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B153" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="C153" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="D153" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="E153" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B154" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="C154" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="D154" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="E154" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B155" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="C155" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="D155" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="E155" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B156" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="C156" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="D156" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="E156" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B157" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="C157" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="D157" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="E157" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B158" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="C158" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="D158" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="E158" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B159" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="C159" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="D159" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="E159" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B160" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="C160" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="D160" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="E160" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B161" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="C161" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="D161" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="E161" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B162" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="C162" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="D162" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="E162" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B163" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="C163" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="D163" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="E163" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B164" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="C164" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="D164" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="E164" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B165" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="C165" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="D165" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="E165" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B166" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="C166" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="D166" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="E166" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B167" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="C167" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="D167" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="E167" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B168" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="C168" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="D168" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="E168" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B169" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="C169" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="D169" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="E169" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B170" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="C170" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="D170" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="E170" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B171" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C171" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="D171" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="E171" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B172" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="C172" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="D172" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="E172" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B173" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="C173" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="D173" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="E173" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B174" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="C174" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="D174" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="E174" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B175" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="C175" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="D175" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="E175" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B176" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="C176" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="D176" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="E176" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B177" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="C177" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="D177" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="E177" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B178" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="C178" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="D178" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E178" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B179" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="C179" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="D179" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="E179" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B180" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="C180" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="D180" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="E180" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B181" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="C181" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="D181" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="E181" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B182" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C182" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="D182" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="E182" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B183" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="C183" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="D183" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="E183" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B184" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="C184" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="D184" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="E184" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="B185" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="C185" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="D185" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="E185" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="B186" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="C186" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="D186" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="E186" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B187" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="C187" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="D187" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="E187" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B188" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="C188" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="D188" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="E188" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B189" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="C189" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="D189" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="E189" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B190" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="C190" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="D190" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="E190" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B191" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="C191" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="D191" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="E191" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B192" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="C192" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="D192" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="E192" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="B193" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="C193" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="D193" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="E193" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="B194" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="C194" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="D194" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="E194" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B195" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="C195" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="D195" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="E195" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B196" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="C196" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="D196" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="E196" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B197" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="C197" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="D197" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="E197" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B198" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="C198" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="D198" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="E198" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B199" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="C199" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="D199" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="E199" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="B200" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="C200" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="D200" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="E200" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="B201" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="C201" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="D201" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="E201" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="B202" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="C202" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="D202" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="E202" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B203" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C203" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="D203" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="E203" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="B204" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C204" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="D204" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="E204" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B205" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="C205" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="D205" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="E205" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="B206" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="C206" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="D206" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="E206" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B207" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="C207" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="D207" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="E207" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="B208" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="C208" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="D208" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="E208" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B209" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="C209" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="D209" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="E209" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B210" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="C210" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="D210" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="E210" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="B211" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="C211" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="D211" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="E211" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="B212" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="C212" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="D212" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="E212" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B213" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="C213" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="D213" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="E213" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="B214" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="C214" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="D214" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="E214" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="B215" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="C215" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="D215" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="E215" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="B216" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="C216" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="D216" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="E216" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B217" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="C217" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="D217" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="E217" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
   </sheetData>
@@ -14980,10 +14980,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -15295,30 +15295,30 @@
         <v>721</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1882</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1883</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1884</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1885</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1886</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="B2" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="C2" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="E2" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -15326,47 +15326,47 @@
         <v>751</v>
       </c>
       <c r="B3" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="C3" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="D3" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E3" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="B4" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="C4" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="D4" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="B5" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="C5" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="D5" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E5" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -15374,16 +15374,16 @@
         <v>752</v>
       </c>
       <c r="B6" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="C6" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="D6" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E6" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -15391,16 +15391,16 @@
         <v>760</v>
       </c>
       <c r="B7" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="C7" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="D7" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E7" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -15408,50 +15408,50 @@
         <v>753</v>
       </c>
       <c r="B8" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="C8" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="D8" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E8" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="B9" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="C9" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="D9" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E9" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="B10" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="C10" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="D10" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E10" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -15459,30 +15459,30 @@
         <v>758</v>
       </c>
       <c r="B11" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="C11" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="D11" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="B12" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="C12" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="D12" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E12" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -15490,30 +15490,30 @@
         <v>756</v>
       </c>
       <c r="B13" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="C13" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="D13" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="B14" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="C14" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="D14" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E14" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -15521,47 +15521,47 @@
         <v>757</v>
       </c>
       <c r="B15" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="C15" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="D15" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E15" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="B16" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="C16" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="E16" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="B17" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="C17" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="D17" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E17" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -15569,50 +15569,50 @@
         <v>761</v>
       </c>
       <c r="B18" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="C18" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="D18" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E18" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="B19" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="C19" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="D19" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E19" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="B20" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="C20" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="D20" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E20" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -15620,33 +15620,33 @@
         <v>750</v>
       </c>
       <c r="B21" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="C21" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="D21" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E21" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="B22" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="C22" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="D22" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E22" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -15654,120 +15654,120 @@
         <v>754</v>
       </c>
       <c r="B23" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="C23" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="D23" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E23" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="B24" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="C24" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="D24" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E24" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="B25" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="C25" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="D25" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E25" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="B26" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="C26" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="D26" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="B27" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="C27" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="D27" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="B28" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="C28" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="D28" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="B29" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="C29" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="D29" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="B30" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="C30" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="D30" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -15775,112 +15775,112 @@
         <v>748</v>
       </c>
       <c r="B31" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="C31" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="D31" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="E31" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="B32" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="C32" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="D32" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="E32" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="B33" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="C33" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="D33" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="E33" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="B34" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="C34" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="D34" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="E34" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="B35" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="C35" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="D35" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="B36" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="C36" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="D36" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="E36" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="B37" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="C37" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="D37" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -15888,16 +15888,16 @@
         <v>749</v>
       </c>
       <c r="B38" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="C38" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="D38" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="E38" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -15905,64 +15905,64 @@
         <v>739</v>
       </c>
       <c r="B39" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="C39" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="D39" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="E39" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="B40" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="C40" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="D40" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="B41" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="C41" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="D41" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="E41" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="B42" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="C42" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="D42" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="E42" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -15970,13 +15970,13 @@
         <v>747</v>
       </c>
       <c r="B43" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="C43" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="D43" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -15984,13 +15984,13 @@
         <v>746</v>
       </c>
       <c r="B44" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="C44" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="D44" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -15998,27 +15998,27 @@
         <v>729</v>
       </c>
       <c r="B45" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="C45" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="D45" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="B46" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="C46" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="D46" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -16026,16 +16026,16 @@
         <v>728</v>
       </c>
       <c r="B47" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="C47" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="D47" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="E47" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -16043,13 +16043,13 @@
         <v>738</v>
       </c>
       <c r="B48" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="C48" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="D48" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
@@ -16057,13 +16057,13 @@
         <v>736</v>
       </c>
       <c r="B49" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="C49" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="D49" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
@@ -16071,27 +16071,27 @@
         <v>737</v>
       </c>
       <c r="B50" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="C50" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="D50" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="B51" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="C51" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="D51" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
@@ -16099,13 +16099,13 @@
         <v>734</v>
       </c>
       <c r="B52" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="C52" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="D52" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
@@ -16113,27 +16113,27 @@
         <v>735</v>
       </c>
       <c r="B53" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="C53" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="D53" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="B54" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="C54" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="D54" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -16141,13 +16141,13 @@
         <v>730</v>
       </c>
       <c r="B55" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="C55" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="D55" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
@@ -16155,13 +16155,13 @@
         <v>732</v>
       </c>
       <c r="B56" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="C56" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="D56" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
@@ -16169,13 +16169,13 @@
         <v>733</v>
       </c>
       <c r="B57" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="C57" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="D57" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
@@ -16183,55 +16183,55 @@
         <v>731</v>
       </c>
       <c r="B58" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="C58" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="D58" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="B59" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="C59" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="D59" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="B60" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="C60" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="D60" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="B61" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="C61" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="D61" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
@@ -16239,30 +16239,30 @@
         <v>740</v>
       </c>
       <c r="B62" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="C62" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="D62" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="E62" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="B63" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="C63" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="D63" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
@@ -16270,13 +16270,13 @@
         <v>743</v>
       </c>
       <c r="B64" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="C64" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D64" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
@@ -16284,13 +16284,13 @@
         <v>742</v>
       </c>
       <c r="B65" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="C65" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="D65" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
@@ -16298,16 +16298,16 @@
         <v>745</v>
       </c>
       <c r="B66" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="C66" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="D66" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="E66" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
@@ -16315,13 +16315,13 @@
         <v>744</v>
       </c>
       <c r="B67" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="C67" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D67" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
@@ -16329,16 +16329,16 @@
         <v>755</v>
       </c>
       <c r="B68" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="C68" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="D68" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="E68" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
@@ -16346,16 +16346,16 @@
         <v>759</v>
       </c>
       <c r="B69" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="C69" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="D69" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="E69" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
     </row>
   </sheetData>
@@ -22572,7 +22572,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -22619,7 +22619,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
@@ -22666,7 +22666,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
@@ -22713,7 +22713,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -22760,7 +22760,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
@@ -22807,7 +22807,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
@@ -22854,7 +22854,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -22901,7 +22901,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -22948,7 +22948,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
@@ -22995,7 +22995,7 @@
         <v>1</v>
       </c>
       <c r="O11" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -23042,7 +23042,7 @@
         <v>1</v>
       </c>
       <c r="O12" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
@@ -23089,7 +23089,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
@@ -23136,7 +23136,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
@@ -23183,7 +23183,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
@@ -23230,7 +23230,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
@@ -23277,7 +23277,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
@@ -23315,7 +23315,7 @@
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -23324,7 +23324,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
@@ -23362,7 +23362,7 @@
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -23371,7 +23371,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
@@ -23418,7 +23418,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
@@ -23465,7 +23465,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
@@ -23512,7 +23512,7 @@
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
@@ -23559,7 +23559,7 @@
         <v>0</v>
       </c>
       <c r="O23" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
@@ -23606,7 +23606,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
@@ -23653,7 +23653,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
@@ -23700,7 +23700,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
@@ -23738,7 +23738,7 @@
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="M27">
         <v>1</v>
@@ -23747,7 +23747,7 @@
         <v>1</v>
       </c>
       <c r="O27" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.2">
@@ -23785,7 +23785,7 @@
         <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="M28">
         <v>1</v>
@@ -23794,7 +23794,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
@@ -23832,7 +23832,7 @@
         <v>1</v>
       </c>
       <c r="L29" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="M29">
         <v>1</v>
@@ -23841,7 +23841,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.2">
@@ -23879,7 +23879,7 @@
         <v>1</v>
       </c>
       <c r="L30" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="M30">
         <v>1</v>
@@ -23888,7 +23888,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.2">
@@ -23935,7 +23935,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.2">
@@ -23982,7 +23982,7 @@
         <v>0</v>
       </c>
       <c r="O32" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.2">
@@ -24029,7 +24029,7 @@
         <v>0</v>
       </c>
       <c r="O33" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.2">
@@ -24076,54 +24076,55 @@
         <v>0</v>
       </c>
       <c r="O34" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="C35" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D35" s="3">
+        <v>99</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="I35" s="3">
+        <f>500*1000000</f>
+        <v>500000000</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>2042</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0.96</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="M35" s="3">
+        <v>99</v>
+      </c>
+      <c r="N35" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3" t="s">
         <v>835</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>197</v>
-      </c>
-      <c r="B35" t="s">
-        <v>749</v>
-      </c>
-      <c r="C35" t="b">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>99</v>
-      </c>
-      <c r="E35" t="s">
-        <v>353</v>
-      </c>
-      <c r="F35" t="s">
-        <v>353</v>
-      </c>
-      <c r="G35" t="s">
-        <v>766</v>
-      </c>
-      <c r="H35" t="s">
-        <v>794</v>
-      </c>
-      <c r="I35">
-        <v>500</v>
-      </c>
-      <c r="J35" t="s">
-        <v>805</v>
-      </c>
-      <c r="K35">
-        <v>0.96</v>
-      </c>
-      <c r="L35" t="s">
-        <v>353</v>
-      </c>
-      <c r="M35">
-        <v>99</v>
-      </c>
-      <c r="N35" t="b">
-        <v>0</v>
-      </c>
-      <c r="O35" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.2">
@@ -24170,7 +24171,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.2">
@@ -24202,7 +24203,7 @@
         <v>-31</v>
       </c>
       <c r="J37" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -24217,7 +24218,7 @@
         <v>0</v>
       </c>
       <c r="O37" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.2">
@@ -24264,7 +24265,7 @@
         <v>0</v>
       </c>
       <c r="O38" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.2">
@@ -24311,7 +24312,7 @@
         <v>0</v>
       </c>
       <c r="O39" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.2">
@@ -24343,7 +24344,7 @@
         <v>-1</v>
       </c>
       <c r="J40" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="K40">
         <v>1</v>
@@ -24358,7 +24359,7 @@
         <v>0</v>
       </c>
       <c r="O40" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.2">
@@ -24390,7 +24391,7 @@
         <v>-1</v>
       </c>
       <c r="J41" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="K41">
         <v>1</v>
@@ -24405,7 +24406,7 @@
         <v>0</v>
       </c>
       <c r="O41" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.2">
@@ -24437,7 +24438,7 @@
         <v>350</v>
       </c>
       <c r="J42" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="K42">
         <v>1</v>
@@ -24452,7 +24453,7 @@
         <v>0</v>
       </c>
       <c r="O42" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.2">
@@ -24484,7 +24485,7 @@
         <v>385</v>
       </c>
       <c r="J43" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="K43">
         <v>1</v>
@@ -24499,7 +24500,7 @@
         <v>0</v>
       </c>
       <c r="O43" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
@@ -24546,7 +24547,7 @@
         <v>0</v>
       </c>
       <c r="O44" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.2">
@@ -24593,7 +24594,7 @@
         <v>0</v>
       </c>
       <c r="O45" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.2">
@@ -24601,7 +24602,7 @@
         <v>208</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="C46" s="3" t="b">
         <v>1</v>
@@ -24640,7 +24641,7 @@
         <v>0</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.2">
@@ -24687,7 +24688,7 @@
         <v>0</v>
       </c>
       <c r="O47" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.2">
@@ -24734,7 +24735,7 @@
         <v>0</v>
       </c>
       <c r="O48" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
@@ -24781,7 +24782,7 @@
         <v>0</v>
       </c>
       <c r="O49" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
@@ -24813,7 +24814,7 @@
         <v>10</v>
       </c>
       <c r="J50" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="K50">
         <v>1</v>
@@ -24828,7 +24829,7 @@
         <v>0</v>
       </c>
       <c r="O50" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
   </sheetData>
@@ -24849,19 +24850,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>848</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>849</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>721</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>850</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -24869,7 +24870,7 @@
         <v>182</v>
       </c>
       <c r="B2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C2" t="s">
         <v>736</v>
@@ -24886,7 +24887,7 @@
         <v>183</v>
       </c>
       <c r="B3" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C3" t="s">
         <v>737</v>
@@ -24903,7 +24904,7 @@
         <v>184</v>
       </c>
       <c r="B4" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C4" t="s">
         <v>737</v>
@@ -24920,7 +24921,7 @@
         <v>185</v>
       </c>
       <c r="B5" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C5" t="s">
         <v>738</v>
@@ -24937,7 +24938,7 @@
         <v>164</v>
       </c>
       <c r="B6" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C6" t="s">
         <v>728</v>
@@ -24954,7 +24955,7 @@
         <v>165</v>
       </c>
       <c r="B7" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C7" t="s">
         <v>728</v>
@@ -24971,7 +24972,7 @@
         <v>166</v>
       </c>
       <c r="B8" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C8" t="s">
         <v>728</v>
@@ -24988,7 +24989,7 @@
         <v>167</v>
       </c>
       <c r="B9" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C9" t="s">
         <v>728</v>
@@ -25005,7 +25006,7 @@
         <v>168</v>
       </c>
       <c r="B10" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C10" t="s">
         <v>728</v>
@@ -25022,7 +25023,7 @@
         <v>169</v>
       </c>
       <c r="B11" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C11" t="s">
         <v>728</v>
@@ -25039,7 +25040,7 @@
         <v>170</v>
       </c>
       <c r="B12" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C12" t="s">
         <v>729</v>
@@ -25068,18 +25069,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>855</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B2">
         <v>2.2546900000000001E-4</v>
@@ -25090,7 +25091,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B3">
         <v>2.2546900000000001E-4</v>
@@ -25101,7 +25102,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B4">
         <v>2.2546900000000001E-4</v>
@@ -25112,7 +25113,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B5">
         <v>2.2546900000000001E-4</v>
@@ -25123,7 +25124,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B6">
         <v>2.2546900000000001E-4</v>
@@ -25134,7 +25135,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B7">
         <v>1.8789100000000001E-4</v>
@@ -25145,7 +25146,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B8">
         <v>1.8789100000000001E-4</v>
@@ -25156,7 +25157,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B9">
         <v>2.2546900000000001E-4</v>
@@ -25167,7 +25168,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B10">
         <v>1.8789100000000001E-4</v>
@@ -25178,7 +25179,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B11">
         <v>2.2546900000000001E-4</v>
@@ -25189,7 +25190,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B12">
         <v>2.2546900000000001E-4</v>
@@ -25200,7 +25201,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B13">
         <v>2.2546900000000001E-4</v>
@@ -25211,7 +25212,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B14">
         <v>2.2546900000000001E-4</v>
@@ -25222,7 +25223,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B15">
         <v>2.2546900000000001E-4</v>
@@ -25233,7 +25234,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B16">
         <v>2.2546900000000001E-4</v>
@@ -25244,7 +25245,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B17">
         <v>2.2546900000000001E-4</v>
@@ -25255,7 +25256,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B18">
         <v>2.2546900000000001E-4</v>
@@ -25266,7 +25267,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B19">
         <v>1.8789100000000001E-4</v>
@@ -25277,7 +25278,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B20">
         <v>2.2546900000000001E-4</v>
@@ -25288,7 +25289,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B21">
         <v>2.2546900000000001E-4</v>
@@ -25299,7 +25300,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B22">
         <v>2.2546900000000001E-4</v>
@@ -25310,7 +25311,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B23">
         <v>2.2546900000000001E-4</v>
@@ -25321,7 +25322,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B24">
         <v>2.2546900000000001E-4</v>
@@ -25332,7 +25333,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B25">
         <v>2.2546900000000001E-4</v>
@@ -25343,7 +25344,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B26">
         <v>2.2546900000000001E-4</v>
@@ -25354,7 +25355,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B27">
         <v>2.2546900000000001E-4</v>
@@ -25365,7 +25366,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B28">
         <v>1.8789100000000001E-4</v>
@@ -25376,7 +25377,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B29">
         <v>1.8789100000000001E-4</v>
@@ -25387,7 +25388,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B30">
         <v>1.8789100000000001E-4</v>
@@ -25413,10 +25414,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>886</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -25724,15 +25725,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B2">
         <v>238642706</v>
@@ -25740,7 +25741,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B3">
         <v>1373628</v>
@@ -25748,7 +25749,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B4">
         <v>1022278</v>
@@ -25756,7 +25757,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B5">
         <v>528573</v>
@@ -25764,7 +25765,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B6">
         <v>22580771</v>
@@ -25772,7 +25773,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B7">
         <v>805952550</v>
@@ -25780,7 +25781,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B8">
         <v>93837413</v>
@@ -25788,7 +25789,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B9">
         <v>177671950</v>
@@ -25796,7 +25797,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B10">
         <v>16932806</v>
@@ -25804,7 +25805,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B11">
         <v>45200741</v>
@@ -25812,7 +25813,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B12">
         <v>11590349</v>
@@ -25820,7 +25821,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B13">
         <v>39651060</v>
@@ -25828,7 +25829,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B14">
         <v>3557266</v>
@@ -25836,7 +25837,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B15">
         <v>798160</v>
@@ -25844,7 +25845,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B16">
         <v>8610160</v>
@@ -25852,7 +25853,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B17">
         <v>6287227</v>
@@ -25860,7 +25861,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B18">
         <v>524875772</v>
@@ -25868,7 +25869,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B19">
         <v>5720335</v>
@@ -25876,7 +25877,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B20">
         <v>18054330</v>
@@ -25884,7 +25885,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B21">
         <v>46875700</v>
@@ -25892,7 +25893,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B22">
         <v>173301131</v>
@@ -25900,7 +25901,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B23">
         <v>51156490</v>
@@ -25908,7 +25909,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B24">
         <v>2051679</v>
@@ -25916,7 +25917,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B25">
         <v>9873029</v>
@@ -25924,7 +25925,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B26">
         <v>19783138</v>
@@ -25932,7 +25933,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B27">
         <v>102893843</v>
@@ -25940,7 +25941,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B28">
         <v>524875772</v>
@@ -25966,7 +25967,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>440</v>
@@ -26010,16 +26011,16 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="I2" t="s">
         <v>434</v>
@@ -26030,7 +26031,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B3">
         <v>-100</v>
@@ -26042,16 +26043,16 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="F3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="I3" t="s">
         <v>434</v>
@@ -26074,16 +26075,16 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F4" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="I4" t="s">
         <v>434</v>
@@ -26094,7 +26095,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B5">
         <v>-100</v>
@@ -26106,16 +26107,16 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="F5" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="I5" t="s">
         <v>434</v>
@@ -26143,27 +26144,27 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>904</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="D2" t="s">
         <v>354</v>
@@ -26171,13 +26172,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C3" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D3" t="s">
         <v>354</v>
@@ -26185,13 +26186,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B4" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C4" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D4" t="s">
         <v>354</v>
@@ -26199,436 +26200,436 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B5" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C5" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="D5" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B6" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C6" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="D6" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B7" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C7" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="D7" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B8" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C8" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="D8" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B9" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="C9" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="D9" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B10" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C10" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D10" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B11" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C11" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="D11" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B12" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C12" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="D12" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B13" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C13" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="D13" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B14" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C14" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D14" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B15" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C15" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="D15" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B16" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C16" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="D16" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B17" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C17" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="D17" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B18" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C18" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D18" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B19" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C19" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D19" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B20" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="C20" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="D20" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B21" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C21" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="D21" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B22" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C22" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D22" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B23" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="C23" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D23" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B24" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C24" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="D24" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B25" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C25" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="D25" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B26" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C26" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D26" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B27" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C27" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D27" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B28" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C28" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="D28" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B29" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C29" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D29" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B30" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="C30" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D30" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B31" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C31" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D31" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B32" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="C32" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="D32" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B33" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C33" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D33" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B34" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C34" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D34" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B35" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C35" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D35" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
   </sheetData>

--- a/ssp_modeling/cb/cb_cost_factors/cb_config_params.xlsx
+++ b/ssp_modeling/cb/cb_cost_factors/cb_config_params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_uganda_data/ssp_modeling/cb/cb_cost_factors/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CFFCD7-34BF-8B4F-A3DD-FF52BCDAB7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5AC5ECE-0A6D-F449-AEB0-63A50E16A5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38560" yWindow="-5840" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45840" yWindow="-7140" windowWidth="35700" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,9 @@
     <sheet name="attribute_dim_time_period" sheetId="16" r:id="rId16"/>
     <sheet name="attribute_transformation_code" sheetId="17" r:id="rId17"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">cost_factors!$A$1:$L$160</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -6211,6 +6214,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000000"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -6280,13 +6286,14 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -10708,12 +10715,11 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -11010,6 +11016,166 @@
       </c>
       <c r="B37">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>0.68846153799999987</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>0.67692307599999979</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.66538461399999971</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0.65384615199999963</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>0.64230768999999954</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0.63076922799999946</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>0.61923076599999938</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>0.60769230399999929</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>0.59615384199999921</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>0.58461537999999913</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>0.57307691799999905</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0.56153845599999896</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>0.54999999399999888</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>0.5384615319999988</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>0.52692306999999872</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>0.51538460799999863</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>0.50384614599999855</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>0.49230768399999847</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>0.48076922199999839</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>0.4692307599999983</v>
       </c>
     </row>
   </sheetData>
@@ -14970,7 +15136,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
@@ -15272,6 +15438,166 @@
       </c>
       <c r="B37">
         <v>2050</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>2070</v>
       </c>
     </row>
   </sheetData>
@@ -16370,8 +16696,9 @@
   <cols>
     <col min="1" max="1" width="58.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="48.5" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="56" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.33203125" customWidth="1"/>
+    <col min="5" max="5" width="5" customWidth="1"/>
+    <col min="6" max="6" width="35.6640625" customWidth="1"/>
     <col min="8" max="8" width="41.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -22457,6 +22784,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L160" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="J80" r:id="rId1" location=":~:text=Using%20the%20World%20Bank%20numbers,case%20of%20U.S.%20LMOP%20landfills." xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
@@ -25404,12 +25732,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9" customWidth="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -25704,8 +26033,168 @@
       <c r="A37">
         <v>35</v>
       </c>
-      <c r="B37">
-        <v>0.55000000000000004</v>
+      <c r="B37" s="4">
+        <v>0.54999999899999996</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" s="4">
+        <v>0.53269230599999995</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39" s="4">
+        <v>0.51538461299999994</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" s="4">
+        <v>0.49807691999999992</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" s="4">
+        <v>0.48076922699999991</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42" s="4">
+        <v>0.4634615339999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" s="4">
+        <v>0.44615384099999988</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" s="4">
+        <v>0.42884614799999987</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" s="4">
+        <v>0.41153845499999986</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46" s="4">
+        <v>0.39423076199999985</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" s="4">
+        <v>0.37692306899999983</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48" s="4">
+        <v>0.35961537599999982</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49" s="4">
+        <v>0.34230768299999981</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50" s="4">
+        <v>0.32499998999999979</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51" s="4">
+        <v>0.30769229699999978</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52" s="4">
+        <v>0.29038460399999977</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53" s="4">
+        <v>0.27307691099999976</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54" s="4">
+        <v>0.25576921799999974</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55" s="4">
+        <v>0.23846152499999973</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56" s="4">
+        <v>0.22115383199999972</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57" s="4">
+        <v>0.2038461389999997</v>
       </c>
     </row>
   </sheetData>

--- a/ssp_modeling/cb/cb_cost_factors/cb_config_params.xlsx
+++ b/ssp_modeling/cb/cb_cost_factors/cb_config_params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_uganda_data/ssp_modeling/cb/cb_cost_factors/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexa/Projects/ssp_uganda_data/ssp_modeling/cb/cb_cost_factors/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EE5FCF-F07C-A645-B65B-E640C083F101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7AA21F-1A25-C744-91DF-9CE8EE3F55A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="-7160" windowWidth="37680" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -6387,7 +6387,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
